--- a/upload/limites_lrf.xlsx
+++ b/upload/limites_lrf.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED233161-EEDD-440A-9C7D-EC06DA68ED40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8730"/>
   </bookViews>
   <sheets>
     <sheet name="limites_lrf" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
   <si>
     <t xml:space="preserve">RECEITA CORRENTE LÍQUIDA – RCL (IV) </t>
   </si>
@@ -71,13 +70,16 @@
   </si>
   <si>
     <t>mes_ano_a_mes_ano</t>
+  </si>
+  <si>
+    <t>jan_2025_a_dez_2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -588,10 +590,10 @@
     <cellStyle name="Ênfase5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Ênfase6" xfId="38" builtinId="49" customBuiltin="1"/>
     <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Neutro" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Incorreto" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Neutra" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Nota" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Ruim" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Saída" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Texto de Aviso" xfId="14" builtinId="11" customBuiltin="1"/>
     <cellStyle name="Texto Explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
@@ -931,25 +933,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="89.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="90.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="121.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="42.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="100.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="60.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="54.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="59.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="89.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="90.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="121.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="100.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="60.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="54.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="59.125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="59" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="9.140625" style="1"/>
+    <col min="12" max="13" width="9.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -984,18 +986,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1">
-        <v>109318007711.96001</v>
+        <v>111739462561.63</v>
       </c>
       <c r="C2" s="1">
-        <v>-844405.5</v>
+        <v>11163115.01</v>
       </c>
       <c r="D2" s="1">
-        <v>12049575.5</v>
+        <v>5554676.6799999997</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>4</v>
@@ -1004,33 +1006,33 @@
         <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>109306802541.96001</v>
+        <v>111722744769.94002</v>
       </c>
       <c r="H2" s="1">
-        <v>53034127686.489998</v>
+        <v>53869167715.228004</v>
       </c>
       <c r="I2" s="1">
-        <v>53560333245.559998</v>
+        <v>54744144937.270607</v>
       </c>
       <c r="J2" s="1">
-        <v>50882316583.279999</v>
+        <v>52006937690.407082</v>
       </c>
       <c r="K2" s="1">
-        <v>48204299921</v>
+        <v>49269730443.543549</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1">
-        <v>106688331960.66</v>
+        <v>109318007711.96001</v>
       </c>
       <c r="C3" s="1">
-        <v>19069999.73</v>
+        <v>-844405.5</v>
       </c>
       <c r="D3" s="1">
-        <v>11634838.5</v>
+        <v>12049575.5</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>4</v>
@@ -1039,30 +1041,30 @@
         <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>106657627122.42999</v>
+        <v>109306802541.96001</v>
       </c>
       <c r="H3" s="1">
-        <v>52056327789.269997</v>
+        <v>53034127686.489998</v>
       </c>
       <c r="I3" s="1">
-        <v>52262237289.989998</v>
+        <v>53560333245.559998</v>
       </c>
       <c r="J3" s="1">
-        <v>49649125425.489998</v>
+        <v>50882316583.279999</v>
       </c>
       <c r="K3" s="1">
-        <v>47036013560.989998</v>
+        <v>48204299921</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>103495630628.38</v>
+        <v>106688331960.66</v>
       </c>
       <c r="C4" s="1">
-        <v>18269291.93</v>
+        <v>19069999.73</v>
       </c>
       <c r="D4" s="1">
         <v>11634838.5</v>
@@ -1074,33 +1076,33 @@
         <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>103465726497.95</v>
+        <v>106657627122.42999</v>
       </c>
       <c r="H4" s="1">
-        <v>50492145171.779999</v>
+        <v>52056327789.269997</v>
       </c>
       <c r="I4" s="1">
-        <v>50698205984</v>
+        <v>52262237289.989998</v>
       </c>
       <c r="J4" s="1">
-        <v>48163295684.800003</v>
+        <v>49649125425.489998</v>
       </c>
       <c r="K4" s="1">
-        <v>45628385385.599998</v>
+        <v>47036013560.989998</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1">
-        <v>99192789740.149994</v>
+        <v>103495630628.38</v>
       </c>
       <c r="C5" s="1">
-        <v>56492032.229999997</v>
+        <v>18269291.93</v>
       </c>
       <c r="D5" s="1">
-        <v>19022957</v>
+        <v>11634838.5</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>4</v>
@@ -1109,33 +1111,33 @@
         <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>99117274750.919998</v>
+        <v>103465726497.95</v>
       </c>
       <c r="H5" s="1">
-        <v>49676872959.790001</v>
+        <v>50492145171.779999</v>
       </c>
       <c r="I5" s="1">
-        <v>48567464627.949997</v>
+        <v>50698205984</v>
       </c>
       <c r="J5" s="1">
-        <v>46139091396.550003</v>
+        <v>48163295684.800003</v>
       </c>
       <c r="K5" s="1">
-        <v>43710718165.160004</v>
+        <v>45628385385.599998</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1">
-        <v>95864466156.229996</v>
+        <v>99192789740.149994</v>
       </c>
       <c r="C6" s="1">
-        <v>79853284.640000001</v>
+        <v>56492032.229999997</v>
       </c>
       <c r="D6" s="1">
-        <v>18522957</v>
+        <v>19022957</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>4</v>
@@ -1144,18 +1146,53 @@
         <v>4</v>
       </c>
       <c r="G6" s="1">
+        <v>99117274750.919998</v>
+      </c>
+      <c r="H6" s="1">
+        <v>49676872959.790001</v>
+      </c>
+      <c r="I6" s="1">
+        <v>48567464627.949997</v>
+      </c>
+      <c r="J6" s="1">
+        <v>46139091396.550003</v>
+      </c>
+      <c r="K6" s="1">
+        <v>43710718165.160004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1">
+        <v>95864466156.229996</v>
+      </c>
+      <c r="C7" s="1">
+        <v>79853284.640000001</v>
+      </c>
+      <c r="D7" s="1">
+        <v>18522957</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="1">
         <v>95766089914.589996</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H7" s="1">
         <v>48234855928.120003</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I7" s="1">
         <v>46925384058.150002</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J7" s="1">
         <v>44579114855.239998</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K7" s="1">
         <v>42232845652.330002</v>
       </c>
     </row>
